--- a/diseases/d200/2010-2014.xlsx
+++ b/diseases/d200/2010-2014.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20266,7 +20266,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20505,7 +20505,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21550,7 +21550,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22192,7 +22192,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23073,7 +23073,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23476,7 +23476,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24999,7 +24999,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26283,7 +26283,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26686,7 +26686,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26925,7 +26925,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27567,7 +27567,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27970,7 +27970,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28209,7 +28209,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28851,7 +28851,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29493,7 +29493,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29896,7 +29896,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30777,7 +30777,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31822,7 +31822,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32061,7 +32061,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32464,7 +32464,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32703,7 +32703,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33106,7 +33106,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33345,7 +33345,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33748,7 +33748,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33987,7 +33987,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34390,7 +34390,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34629,7 +34629,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35032,7 +35032,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -35674,7 +35674,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -35913,7 +35913,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36316,7 +36316,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36555,7 +36555,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -36958,7 +36958,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37197,7 +37197,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -37600,7 +37600,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38242,7 +38242,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38481,7 +38481,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -38884,7 +38884,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39123,7 +39123,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
